--- a/saldo_menor/sinais_saldo_menor_2026-08-02.xlsx
+++ b/saldo_menor/sinais_saldo_menor_2026-08-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/saldo_menor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_5955BB5E176861A6C4EA1CD04B5ED87656CDD720" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCBBB533-C2E4-4350-82F2-4DCBE74AE44F}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_5955BB5E176861A6C4EA1CD04B5ED87656CDD720" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB30924E-6AE0-45F1-8D12-A28F2688287D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="117">
   <si>
     <t>Data</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>🟢 Betmines: 1X &amp; UNDER 2.5 (Placar: 1x0 ou 2x0 | Confiança 75.2%)</t>
-  </si>
-  <si>
-    <t>APROVADO_SALDO_MENOR</t>
   </si>
   <si>
     <t>07:30</t>
@@ -466,6 +463,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -753,10 +754,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -794,7 +795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46236</v>
       </c>
@@ -828,34 +829,31 @@
       <c r="K2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
       <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
       </c>
       <c r="H3">
         <v>2.35</v>
@@ -867,36 +865,33 @@
         <v>1.47</v>
       </c>
       <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
       <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
       </c>
       <c r="H4">
         <v>2.15</v>
@@ -908,36 +903,33 @@
         <v>1.96</v>
       </c>
       <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5">
         <v>1.91</v>
@@ -949,36 +941,33 @@
         <v>1.65</v>
       </c>
       <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B6" t="s">
         <v>29</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>2.6</v>
@@ -990,36 +979,33 @@
         <v>1.23</v>
       </c>
       <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
         <v>36</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
       </c>
       <c r="H7">
         <v>2.5499999999999998</v>
@@ -1031,36 +1017,33 @@
         <v>1.88</v>
       </c>
       <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B8" t="s">
         <v>38</v>
       </c>
-      <c r="L7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>41</v>
       </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>2.2000000000000002</v>
@@ -1072,36 +1055,33 @@
         <v>1.47</v>
       </c>
       <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B9" t="s">
         <v>43</v>
       </c>
-      <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>46</v>
       </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9">
         <v>2.0499999999999998</v>
@@ -1113,36 +1093,33 @@
         <v>1.96</v>
       </c>
       <c r="K9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
         <v>48</v>
       </c>
-      <c r="L9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H10">
         <v>2.75</v>
@@ -1154,36 +1131,33 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="K10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B11" t="s">
         <v>52</v>
       </c>
-      <c r="L10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>53</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>54</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>55</v>
       </c>
-      <c r="E11" t="s">
-        <v>56</v>
-      </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11">
         <v>2.57</v>
@@ -1195,36 +1169,33 @@
         <v>1.79</v>
       </c>
       <c r="K11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B12" t="s">
         <v>57</v>
       </c>
-      <c r="L11" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>58</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>60</v>
       </c>
-      <c r="E12" t="s">
-        <v>61</v>
-      </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12">
         <v>2.15</v>
@@ -1236,36 +1207,33 @@
         <v>1.56</v>
       </c>
       <c r="K12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
         <v>62</v>
       </c>
-      <c r="L12" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>63</v>
       </c>
-      <c r="E13" t="s">
-        <v>64</v>
-      </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H13">
         <v>2.2000000000000002</v>
@@ -1277,36 +1245,33 @@
         <v>1.3</v>
       </c>
       <c r="K13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
       </c>
-      <c r="L13" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>66</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>68</v>
       </c>
-      <c r="E14" t="s">
-        <v>69</v>
-      </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H14">
         <v>1.73</v>
@@ -1318,36 +1283,33 @@
         <v>1.7</v>
       </c>
       <c r="K14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B15" t="s">
         <v>70</v>
       </c>
-      <c r="L14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>71</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>72</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>73</v>
       </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
       <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" t="s">
         <v>73</v>
-      </c>
-      <c r="G15" t="s">
-        <v>74</v>
       </c>
       <c r="H15">
         <v>2.3199999999999998</v>
@@ -1359,36 +1321,33 @@
         <v>1.88</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>46236</v>
       </c>
       <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>76</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>77</v>
       </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
       <c r="F16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
         <v>77</v>
-      </c>
-      <c r="G16" t="s">
-        <v>78</v>
       </c>
       <c r="H16">
         <v>2.4500000000000002</v>
@@ -1400,36 +1359,33 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="K16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
         <v>79</v>
       </c>
-      <c r="L16" t="s">
-        <v>17</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>80</v>
       </c>
-      <c r="E17" t="s">
-        <v>81</v>
-      </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H17">
         <v>2.0499999999999998</v>
@@ -1441,36 +1397,33 @@
         <v>1.05</v>
       </c>
       <c r="K17" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B18" t="s">
         <v>82</v>
       </c>
-      <c r="L17" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>83</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>84</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>85</v>
       </c>
-      <c r="E18" t="s">
-        <v>86</v>
-      </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H18">
         <v>2.2000000000000002</v>
@@ -1482,36 +1435,33 @@
         <v>0.98</v>
       </c>
       <c r="K18" t="s">
+        <v>86</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
         <v>87</v>
       </c>
-      <c r="L18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>88</v>
       </c>
-      <c r="E19" t="s">
-        <v>89</v>
-      </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H19">
         <v>2.15</v>
@@ -1523,36 +1473,33 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="K19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
         <v>90</v>
       </c>
-      <c r="L19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>91</v>
       </c>
-      <c r="E20" t="s">
-        <v>92</v>
-      </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H20">
         <v>2.2000000000000002</v>
@@ -1564,36 +1511,33 @@
         <v>1</v>
       </c>
       <c r="K20" t="s">
+        <v>92</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
         <v>93</v>
       </c>
-      <c r="L20" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>94</v>
       </c>
-      <c r="E21" t="s">
-        <v>95</v>
-      </c>
       <c r="F21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H21">
         <v>2.4500000000000002</v>
@@ -1605,36 +1549,33 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="K21" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>46236</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" t="s">
         <v>96</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>97</v>
       </c>
-      <c r="E22" t="s">
-        <v>98</v>
-      </c>
       <c r="F22" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" t="s">
         <v>97</v>
-      </c>
-      <c r="G22" t="s">
-        <v>98</v>
       </c>
       <c r="H22">
         <v>2.44</v>
@@ -1646,36 +1587,33 @@
         <v>1.25</v>
       </c>
       <c r="K22" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
         <v>99</v>
       </c>
-      <c r="L22" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>100</v>
       </c>
-      <c r="E23" t="s">
-        <v>101</v>
-      </c>
       <c r="F23" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" t="s">
         <v>100</v>
-      </c>
-      <c r="G23" t="s">
-        <v>101</v>
       </c>
       <c r="H23">
         <v>2.52</v>
@@ -1687,36 +1625,33 @@
         <v>1.3</v>
       </c>
       <c r="K23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
         <v>102</v>
       </c>
-      <c r="L23" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>103</v>
       </c>
-      <c r="E24" t="s">
-        <v>104</v>
-      </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H24">
         <v>1.81</v>
@@ -1728,36 +1663,33 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="K24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
         <v>105</v>
       </c>
-      <c r="L24" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>106</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>107</v>
       </c>
-      <c r="E25" t="s">
-        <v>108</v>
-      </c>
       <c r="F25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H25">
         <v>2.25</v>
@@ -1769,36 +1701,33 @@
         <v>1.96</v>
       </c>
       <c r="K25" t="s">
+        <v>108</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>109</v>
       </c>
-      <c r="L25" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>110</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>111</v>
       </c>
-      <c r="E26" t="s">
-        <v>112</v>
-      </c>
       <c r="F26" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" t="s">
         <v>111</v>
-      </c>
-      <c r="G26" t="s">
-        <v>112</v>
       </c>
       <c r="H26">
         <v>2.15</v>
@@ -1810,36 +1739,33 @@
         <v>1.7</v>
       </c>
       <c r="K26" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
         <v>113</v>
       </c>
-      <c r="L26" t="s">
-        <v>17</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>46236</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>114</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>115</v>
       </c>
-      <c r="E27" t="s">
-        <v>116</v>
-      </c>
       <c r="F27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" t="s">
         <v>115</v>
-      </c>
-      <c r="G27" t="s">
-        <v>116</v>
       </c>
       <c r="H27">
         <v>2.2000000000000002</v>
@@ -1851,12 +1777,9 @@
         <v>1.56</v>
       </c>
       <c r="K27" t="s">
-        <v>117</v>
-      </c>
-      <c r="L27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M27">
+        <v>116</v>
+      </c>
+      <c r="L27">
         <v>1</v>
       </c>
     </row>
